--- a/ADDITIONAL_DATA.xlsx
+++ b/ADDITIONAL_DATA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intcap-my.sharepoint.com/personal/divo_pulitika_intercapital_hr/Documents/Desktop/Tradeweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{9E6FC9DA-7D56-4F1E-BC2D-76D340AD8695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A0ABF52-D64B-4214-ADC5-6E9E66A07370}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{9E6FC9DA-7D56-4F1E-BC2D-76D340AD8695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F174B8C-B586-43D6-AEC9-0F762655159E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GENERAL" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>Vijednosni papir Trezorski zapis</t>
   </si>
@@ -212,6 +212,42 @@
   </si>
   <si>
     <t>InterCapital_HRICAMFSBTC7_ICSLOETF</t>
+  </si>
+  <si>
+    <t>LOCATION IN PRINOS FILE</t>
+  </si>
+  <si>
+    <t>BET-TRN_A17</t>
+  </si>
+  <si>
+    <t>BET-TRN_B17</t>
+  </si>
+  <si>
+    <t>CROBEX ETF_C13</t>
+  </si>
+  <si>
+    <t>CROBEX ETF_A13</t>
+  </si>
+  <si>
+    <t>CROBEX ETF_B13</t>
+  </si>
+  <si>
+    <t>RO FI BOND_A19</t>
+  </si>
+  <si>
+    <t>RO FI BOND_B19</t>
+  </si>
+  <si>
+    <t>CASH ETF_A18</t>
+  </si>
+  <si>
+    <t>SBI ETF_A14</t>
+  </si>
+  <si>
+    <t>SBI ETF_C14</t>
+  </si>
+  <si>
+    <t>SBI ETF_B14</t>
   </si>
 </sst>
 </file>
@@ -529,17 +565,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C46E2B-C9E8-4ACD-97D0-105BC9E5EFA4}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.88671875" customWidth="1"/>
-    <col min="2" max="2" width="55.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.6640625" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" customWidth="1"/>
+    <col min="5" max="5" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -555,8 +592,11 @@
       <c r="E1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -572,8 +612,11 @@
       <c r="E2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -589,8 +632,11 @@
       <c r="E3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -606,8 +652,11 @@
       <c r="E4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,8 +672,11 @@
       <c r="E5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -640,8 +692,11 @@
       <c r="E6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -657,8 +712,11 @@
       <c r="E7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -674,8 +732,11 @@
       <c r="E8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -691,8 +752,11 @@
       <c r="E9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -708,8 +772,11 @@
       <c r="E10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -725,8 +792,11 @@
       <c r="E11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -741,6 +811,9 @@
       </c>
       <c r="E12" t="s">
         <v>57</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -751,13 +824,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -765,7 +838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -773,7 +846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -781,7 +854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -789,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -805,19 +878,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7498EE14-A2FD-4658-B40A-C2C444B765D5}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>

--- a/ADDITIONAL_DATA.xlsx
+++ b/ADDITIONAL_DATA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intcap-my.sharepoint.com/personal/divo_pulitika_intercapital_hr/Documents/Desktop/Tradeweb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ĐivoPulitika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{9E6FC9DA-7D56-4F1E-BC2D-76D340AD8695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F174B8C-B586-43D6-AEC9-0F762655159E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D7EF1B-243F-49F7-8D7C-FD658CE6559F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="31785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GENERAL" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
   <si>
     <t>Vijednosni papir Trezorski zapis</t>
   </si>
@@ -248,6 +248,21 @@
   </si>
   <si>
     <t>SBI ETF_B14</t>
+  </si>
+  <si>
+    <t>HRICAMFPWIG3</t>
+  </si>
+  <si>
+    <t>INTERCAPITAL POLAND WIG30TR UCITS ETF</t>
+  </si>
+  <si>
+    <t>7POL</t>
+  </si>
+  <si>
+    <t>InterCapital_HRICAMFPWIG3_7POL</t>
+  </si>
+  <si>
+    <t>POLAND ETF_A20</t>
   </si>
 </sst>
 </file>
@@ -565,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C46E2B-C9E8-4ACD-97D0-105BC9E5EFA4}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -814,6 +829,26 @@
       </c>
       <c r="F12" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
